--- a/assets/docs/lop4/Tin hoc - Lop 4.xlsx
+++ b/assets/docs/lop4/Tin hoc - Lop 4.xlsx
@@ -617,7 +617,8 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): Ở bài “Gõ bàn phím đúng cách”.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): Ở bài “Gõ bàn phím đúng cách”, GV hướng dẫn HS đặt tay đúng hàng phím cơ sở và gõ bằng mười ngón; HS gõ một đoạn ngắn cho sẵn, tự đếm số lỗi
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu hai ảnh tư thế ngồi máy: một đúng, một sai; HS chỉ ra chỗ khác nhau ở lưng, khoảng cách mắt</t>
         </is>
       </c>
     </row>
@@ -741,7 +742,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>AI-NB (Nhận biết): Chỉ cho HS thấy phần trả lời tóm tắt do máy tự sinh đặt ở đầu trang kết quả.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV hướng dẫn HS chọn từ khoá ngắn, đúng trọng tâm cho một câu hỏi cụ thể; HS gõ từ khoá
+Năng lực số Miền 1 (Cơ bản, bậc 2): HS đối chiếu thông tin tìm được ở ít nhất hai trang và với SGK; ghi lại tên trang đã lấy thông tin vào phiếu để biết mình đang tin vào nguồn nào.
+Năng lực số Miền 6 (Cơ bản, bậc 2): GV chỉ cho HS thấy phần trả lời tóm tắt do máy tự sinh đặt ở đầu trang kết quả; nêu rõ đó là do trí tuệ nhân tạo viết</t>
         </is>
       </c>
     </row>
@@ -861,7 +864,8 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS quan sát cửa sổ giấy phép hiện ra khi cài một phần mềm, chỉ chỗ ghi phần mềm dùng miễn phí hay phải mua.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV cho HS quan sát cửa sổ giấy phép hiện ra khi cài một phần mềm, chỉ chỗ ghi phần mềm dùng miễn phí hay phải mua
+Năng lực số Miền 3 (Cơ bản, bậc 2): GV nêu công sức của người viết phần mềm, người vẽ tranh, người viết truyện; HS liên hệ với sản phẩm của chính mình: nếu bài mình làm bị bạn lấy đem nộp thì…</t>
         </is>
       </c>
     </row>
@@ -956,7 +960,8 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): Cho HS so sánh hai trang chiếu cùng nội dung.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): GV cho HS so sánh hai trang chiếu cùng nội dung: một trang chữ nhỏ, nhiều màu loè loẹt và một trang chữ to, màu tương phản rõ
+Năng lực số Miền 3 (Cơ bản, bậc 2): HS định dạng lại bài trình chiếu của mình: chỉnh cỡ chữ tiêu đề và nội dung, chọn màu chữ nổi trên nền, căn lề cho thẳng, bỏ bớt chữ thừa.</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1325,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Chọn phần mềm trò chơi mang tính học tập (xếp hình, luyện gõ, giải đố, tìm đường).</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): GV chọn phần mềm trò chơi mang tính học tập (xếp hình, luyện gõ, giải đố, tìm đường); HS chơi và nêu trò chơi đó rèn cho mình kĩ năng gì
+Năng lực số Miền 2 (Cơ bản, bậc 2): HS thoả thuận với bạn luật chơi và thứ tự lượt khi dùng chung một máy; giữ thái độ vui vẻ khi thắng, bình tĩnh khi thua, không tranh giành chuột và bàn phím.</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1386,8 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Giới thiệu màn hình phần mềm lập trình trực quan.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): GV giới thiệu màn hình phần mềm lập trình trực quan: khu vực khối lệnh, khu vực ghép lệnh, sân khấu và nhân vật; HS kéo thả vài khối lệnh di chuyển, xoay
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS thử đổi thứ tự các khối lệnh rồi chạy lại để thấy máy làm đúng theo thứ tự mình xếp — sai ở đâu sửa ở đó, chạy lại không tốn gì.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1451,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): HS diễn tả một ý tưởng của mình thành chương trình cho “Tạo chương trình máy tính để diễn tả ý tưởng”.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): HS diễn tả một ý tưởng của mình thành chương trình cho “Tạo chương trình máy tính để diễn tả ý tưởng”: chọn nhân vật, phông nền
+Năng lực số Miền 5 (Cơ bản, bậc 2): Khi chương trình chạy chưa đúng, HS chia nhỏ để tìm lỗi: chạy từng phần, kiểm tra thứ tự lệnh, đổi giá trị thời gian và bước đi
+Năng lực số Miền 2 (Cơ bản, bậc 2): HS giới thiệu chương trình của mình trước lớp, nghe bạn góp ý và ghi lại một điều mình sẽ cải tiến ở lần sau.</t>
         </is>
       </c>
     </row>
